--- a/ig/MP-QA/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/ig/MP-QA/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-27T17:46:32+00:00</t>
+    <t>2024-03-27T18:09:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/MP-QA/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/ig/MP-QA/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-27T18:09:18+00:00</t>
+    <t>2024-04-03T15:17:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/MP-QA/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/ig/MP-QA/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T15:17:50+00:00</t>
+    <t>2024-04-08T08:34:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>ANS (https://esante.gouv.fr)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
